--- a/VerveStacks_HRV_grids_kan10/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_HRV_grids_kan10/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_HRV_grids_kan10\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3136E663-A2EB-4E74-A77C-5E37C97B1FA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{59EA20AE-A07A-4DDC-9C38-8A64007E34A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -358,22 +358,22 @@
     <t>e_demand,ev_battery,H2prd_Elc_PEM,H2prd_Elc_ALK</t>
   </si>
   <si>
+    <t>KastelStari_HRV</t>
+  </si>
+  <si>
+    <t>at grid node - KastelStari_HRV</t>
+  </si>
+  <si>
+    <t>Rijeka_HRV</t>
+  </si>
+  <si>
+    <t>at grid node - Rijeka_HRV</t>
+  </si>
+  <si>
     <t>Sibenik_HRV</t>
   </si>
   <si>
     <t>at grid node - Sibenik_HRV</t>
-  </si>
-  <si>
-    <t>KastelStari_HRV</t>
-  </si>
-  <si>
-    <t>at grid node - KastelStari_HRV</t>
-  </si>
-  <si>
-    <t>Rijeka_HRV</t>
-  </si>
-  <si>
-    <t>at grid node - Rijeka_HRV</t>
   </si>
   <si>
     <t>h_demand</t>
@@ -821,10 +821,10 @@
         <v>78</v>
       </c>
       <c r="M11" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="N11" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="O11" t="s">
         <v>105</v>
@@ -871,10 +871,10 @@
         <v>78</v>
       </c>
       <c r="M12" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="N12" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="O12" t="s">
         <v>105</v>
@@ -921,10 +921,10 @@
         <v>78</v>
       </c>
       <c r="M13" t="s">
-        <v>82</v>
+        <v>106</v>
       </c>
       <c r="N13" t="s">
-        <v>83</v>
+        <v>107</v>
       </c>
       <c r="O13" t="s">
         <v>105</v>
@@ -971,10 +971,10 @@
         <v>78</v>
       </c>
       <c r="M14" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="N14" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="O14" t="s">
         <v>105</v>
@@ -1047,10 +1047,10 @@
         <v>78</v>
       </c>
       <c r="M16" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="N16" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="O16" t="s">
         <v>105</v>
@@ -1085,10 +1085,10 @@
         <v>78</v>
       </c>
       <c r="M17" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="N17" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="O17" t="s">
         <v>105</v>
@@ -1111,10 +1111,10 @@
         <v>78</v>
       </c>
       <c r="M18" t="s">
-        <v>99</v>
+        <v>82</v>
       </c>
       <c r="N18" t="s">
-        <v>100</v>
+        <v>83</v>
       </c>
       <c r="O18" t="s">
         <v>105</v>
@@ -1137,10 +1137,10 @@
         <v>78</v>
       </c>
       <c r="M19" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="N19" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="O19" t="s">
         <v>105</v>
@@ -1163,10 +1163,10 @@
         <v>78</v>
       </c>
       <c r="M20" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="N20" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="O20" t="s">
         <v>105</v>
@@ -1215,10 +1215,10 @@
         <v>78</v>
       </c>
       <c r="M22" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="N22" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="O22" t="s">
         <v>105</v>
@@ -1229,10 +1229,10 @@
         <v>78</v>
       </c>
       <c r="M23" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="N23" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="O23" t="s">
         <v>105</v>
@@ -1243,10 +1243,10 @@
         <v>78</v>
       </c>
       <c r="M24" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="N24" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="O24" t="s">
         <v>105</v>
@@ -1257,10 +1257,10 @@
         <v>78</v>
       </c>
       <c r="M25" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="N25" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="O25" t="s">
         <v>105</v>

--- a/VerveStacks_HRV_grids_kan10/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_HRV_grids_kan10/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_HRV_grids_kan10\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{59EA20AE-A07A-4DDC-9C38-8A64007E34A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{AD5BDDF3-9E3A-4B2D-8121-9141C89E2C5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -355,25 +355,25 @@
     <t>at grid node - Knin_HRV</t>
   </si>
   <si>
+    <t>Rijeka_HRV</t>
+  </si>
+  <si>
+    <t>at grid node - Rijeka_HRV</t>
+  </si>
+  <si>
     <t>e_demand,ev_battery,H2prd_Elc_PEM,H2prd_Elc_ALK</t>
   </si>
   <si>
+    <t>Sibenik_HRV</t>
+  </si>
+  <si>
+    <t>at grid node - Sibenik_HRV</t>
+  </si>
+  <si>
     <t>KastelStari_HRV</t>
   </si>
   <si>
     <t>at grid node - KastelStari_HRV</t>
-  </si>
-  <si>
-    <t>Rijeka_HRV</t>
-  </si>
-  <si>
-    <t>at grid node - Rijeka_HRV</t>
-  </si>
-  <si>
-    <t>Sibenik_HRV</t>
-  </si>
-  <si>
-    <t>at grid node - Sibenik_HRV</t>
   </si>
   <si>
     <t>h_demand</t>
@@ -821,13 +821,13 @@
         <v>78</v>
       </c>
       <c r="M11" t="s">
-        <v>89</v>
+        <v>105</v>
       </c>
       <c r="N11" t="s">
-        <v>90</v>
+        <v>106</v>
       </c>
       <c r="O11" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="Q11" t="s">
         <v>78</v>
@@ -871,13 +871,13 @@
         <v>78</v>
       </c>
       <c r="M12" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="N12" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="O12" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="Q12" t="s">
         <v>78</v>
@@ -921,13 +921,13 @@
         <v>78</v>
       </c>
       <c r="M13" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="N13" t="s">
+        <v>100</v>
+      </c>
+      <c r="O13" t="s">
         <v>107</v>
-      </c>
-      <c r="O13" t="s">
-        <v>105</v>
       </c>
       <c r="Q13" t="s">
         <v>78</v>
@@ -971,13 +971,13 @@
         <v>78</v>
       </c>
       <c r="M14" t="s">
-        <v>108</v>
+        <v>79</v>
       </c>
       <c r="N14" t="s">
-        <v>109</v>
+        <v>80</v>
       </c>
       <c r="O14" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="Q14" t="s">
         <v>78</v>
@@ -1009,13 +1009,13 @@
         <v>78</v>
       </c>
       <c r="M15" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="N15" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="O15" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="Q15" t="s">
         <v>78</v>
@@ -1047,13 +1047,13 @@
         <v>78</v>
       </c>
       <c r="M16" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="N16" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="O16" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="Q16" t="s">
         <v>78</v>
@@ -1085,13 +1085,13 @@
         <v>78</v>
       </c>
       <c r="M17" t="s">
-        <v>84</v>
+        <v>101</v>
       </c>
       <c r="N17" t="s">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="O17" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="18" spans="7:15" x14ac:dyDescent="0.45">
@@ -1111,13 +1111,13 @@
         <v>78</v>
       </c>
       <c r="M18" t="s">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="N18" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="O18" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="19" spans="7:15" x14ac:dyDescent="0.45">
@@ -1137,13 +1137,13 @@
         <v>78</v>
       </c>
       <c r="M19" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="N19" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="O19" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="20" spans="7:15" x14ac:dyDescent="0.45">
@@ -1163,13 +1163,13 @@
         <v>78</v>
       </c>
       <c r="M20" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="N20" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="O20" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="21" spans="7:15" x14ac:dyDescent="0.45">
@@ -1195,7 +1195,7 @@
         <v>111</v>
       </c>
       <c r="O21" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="22" spans="7:15" x14ac:dyDescent="0.45">
@@ -1215,13 +1215,13 @@
         <v>78</v>
       </c>
       <c r="M22" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="N22" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="O22" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="23" spans="7:15" x14ac:dyDescent="0.45">
@@ -1229,13 +1229,13 @@
         <v>78</v>
       </c>
       <c r="M23" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="N23" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="O23" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="24" spans="7:15" x14ac:dyDescent="0.45">
@@ -1243,13 +1243,13 @@
         <v>78</v>
       </c>
       <c r="M24" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="N24" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="O24" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="25" spans="7:15" x14ac:dyDescent="0.45">
@@ -1263,7 +1263,7 @@
         <v>98</v>
       </c>
       <c r="O25" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
   </sheetData>

--- a/VerveStacks_HRV_grids_kan10/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_HRV_grids_kan10/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_HRV_grids_kan10\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AD5BDDF3-9E3A-4B2D-8121-9141C89E2C5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A31F87BA-CD46-4E2A-9337-6F62CED5527F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -355,25 +355,25 @@
     <t>at grid node - Knin_HRV</t>
   </si>
   <si>
+    <t>e_demand,ev_battery,H2prd_Elc_PEM,H2prd_Elc_ALK</t>
+  </si>
+  <si>
     <t>Rijeka_HRV</t>
   </si>
   <si>
     <t>at grid node - Rijeka_HRV</t>
   </si>
   <si>
-    <t>e_demand,ev_battery,H2prd_Elc_PEM,H2prd_Elc_ALK</t>
+    <t>KastelStari_HRV</t>
+  </si>
+  <si>
+    <t>at grid node - KastelStari_HRV</t>
   </si>
   <si>
     <t>Sibenik_HRV</t>
   </si>
   <si>
     <t>at grid node - Sibenik_HRV</t>
-  </si>
-  <si>
-    <t>KastelStari_HRV</t>
-  </si>
-  <si>
-    <t>at grid node - KastelStari_HRV</t>
   </si>
   <si>
     <t>h_demand</t>
@@ -821,13 +821,13 @@
         <v>78</v>
       </c>
       <c r="M11" t="s">
+        <v>79</v>
+      </c>
+      <c r="N11" t="s">
+        <v>80</v>
+      </c>
+      <c r="O11" t="s">
         <v>105</v>
-      </c>
-      <c r="N11" t="s">
-        <v>106</v>
-      </c>
-      <c r="O11" t="s">
-        <v>107</v>
       </c>
       <c r="Q11" t="s">
         <v>78</v>
@@ -871,13 +871,13 @@
         <v>78</v>
       </c>
       <c r="M12" t="s">
-        <v>84</v>
+        <v>99</v>
       </c>
       <c r="N12" t="s">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="O12" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="Q12" t="s">
         <v>78</v>
@@ -921,13 +921,13 @@
         <v>78</v>
       </c>
       <c r="M13" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="N13" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="O13" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="Q13" t="s">
         <v>78</v>
@@ -971,13 +971,13 @@
         <v>78</v>
       </c>
       <c r="M14" t="s">
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="N14" t="s">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="O14" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="Q14" t="s">
         <v>78</v>
@@ -1009,13 +1009,13 @@
         <v>78</v>
       </c>
       <c r="M15" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="N15" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="O15" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="Q15" t="s">
         <v>78</v>
@@ -1047,13 +1047,13 @@
         <v>78</v>
       </c>
       <c r="M16" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="N16" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="O16" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="Q16" t="s">
         <v>78</v>
@@ -1085,13 +1085,13 @@
         <v>78</v>
       </c>
       <c r="M17" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="N17" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="O17" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="18" spans="7:15" x14ac:dyDescent="0.45">
@@ -1111,13 +1111,13 @@
         <v>78</v>
       </c>
       <c r="M18" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="N18" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="O18" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="19" spans="7:15" x14ac:dyDescent="0.45">
@@ -1137,13 +1137,13 @@
         <v>78</v>
       </c>
       <c r="M19" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="N19" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="O19" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="20" spans="7:15" x14ac:dyDescent="0.45">
@@ -1163,13 +1163,13 @@
         <v>78</v>
       </c>
       <c r="M20" t="s">
-        <v>108</v>
+        <v>86</v>
       </c>
       <c r="N20" t="s">
-        <v>109</v>
+        <v>87</v>
       </c>
       <c r="O20" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="21" spans="7:15" x14ac:dyDescent="0.45">
@@ -1189,13 +1189,13 @@
         <v>78</v>
       </c>
       <c r="M21" t="s">
-        <v>110</v>
+        <v>91</v>
       </c>
       <c r="N21" t="s">
-        <v>111</v>
+        <v>92</v>
       </c>
       <c r="O21" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="22" spans="7:15" x14ac:dyDescent="0.45">
@@ -1215,13 +1215,13 @@
         <v>78</v>
       </c>
       <c r="M22" t="s">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="N22" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="O22" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="23" spans="7:15" x14ac:dyDescent="0.45">
@@ -1229,13 +1229,13 @@
         <v>78</v>
       </c>
       <c r="M23" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="N23" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="O23" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="24" spans="7:15" x14ac:dyDescent="0.45">
@@ -1243,13 +1243,13 @@
         <v>78</v>
       </c>
       <c r="M24" t="s">
-        <v>86</v>
+        <v>110</v>
       </c>
       <c r="N24" t="s">
-        <v>87</v>
+        <v>111</v>
       </c>
       <c r="O24" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="25" spans="7:15" x14ac:dyDescent="0.45">
@@ -1257,13 +1257,13 @@
         <v>78</v>
       </c>
       <c r="M25" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="N25" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="O25" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
   </sheetData>

--- a/VerveStacks_HRV_grids_kan10/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_HRV_grids_kan10/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_HRV_grids_kan10\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A31F87BA-CD46-4E2A-9337-6F62CED5527F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D6AB895F-B599-4116-AA74-B9AD03C78F4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="114">
   <si>
     <t>PSET_PN</t>
   </si>
@@ -358,25 +358,28 @@
     <t>e_demand,ev_battery,H2prd_Elc_PEM,H2prd_Elc_ALK</t>
   </si>
   <si>
+    <t>Sibenik_HRV</t>
+  </si>
+  <si>
+    <t>at grid node - Sibenik_HRV</t>
+  </si>
+  <si>
+    <t>KastelStari_HRV</t>
+  </si>
+  <si>
+    <t>at grid node - KastelStari_HRV</t>
+  </si>
+  <si>
     <t>Rijeka_HRV</t>
   </si>
   <si>
     <t>at grid node - Rijeka_HRV</t>
   </si>
   <si>
-    <t>KastelStari_HRV</t>
-  </si>
-  <si>
-    <t>at grid node - KastelStari_HRV</t>
-  </si>
-  <si>
-    <t>Sibenik_HRV</t>
-  </si>
-  <si>
-    <t>at grid node - Sibenik_HRV</t>
-  </si>
-  <si>
     <t>h_demand</t>
+  </si>
+  <si>
+    <t>en_hop_gas_boiler,en_hop_biomass_chips,en_hop_electric_boiler,en_hp_air_10mw</t>
   </si>
 </sst>
 </file>
@@ -704,15 +707,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{268E9BAB-B98F-4B82-9042-51EABC9ED525}">
-  <dimension ref="B3:T25"/>
+  <dimension ref="B3:Y25"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="3" spans="2:20" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B3" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="4" spans="2:20" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B4" t="s">
         <v>21</v>
       </c>
@@ -720,7 +723,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="5" spans="2:20" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B5" t="s">
         <v>44</v>
       </c>
@@ -728,7 +731,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="2:20" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B9" t="s">
         <v>70</v>
       </c>
@@ -741,8 +744,11 @@
       <c r="Q9" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="10" spans="2:20" x14ac:dyDescent="0.45">
+      <c r="V9" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="10" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B10" t="s">
         <v>32</v>
       </c>
@@ -791,8 +797,20 @@
       <c r="T10" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="11" spans="2:20" x14ac:dyDescent="0.45">
+      <c r="V10" t="s">
+        <v>32</v>
+      </c>
+      <c r="W10" t="s">
+        <v>71</v>
+      </c>
+      <c r="X10" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y10" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B11" t="s">
         <v>78</v>
       </c>
@@ -821,10 +839,10 @@
         <v>78</v>
       </c>
       <c r="M11" t="s">
-        <v>79</v>
+        <v>101</v>
       </c>
       <c r="N11" t="s">
-        <v>80</v>
+        <v>102</v>
       </c>
       <c r="O11" t="s">
         <v>105</v>
@@ -841,8 +859,20 @@
       <c r="T11" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="12" spans="2:20" x14ac:dyDescent="0.45">
+      <c r="V11" t="s">
+        <v>78</v>
+      </c>
+      <c r="W11" t="s">
+        <v>79</v>
+      </c>
+      <c r="X11" t="s">
+        <v>80</v>
+      </c>
+      <c r="Y11" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="12" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B12" t="s">
         <v>78</v>
       </c>
@@ -871,10 +901,10 @@
         <v>78</v>
       </c>
       <c r="M12" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="N12" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="O12" t="s">
         <v>105</v>
@@ -891,8 +921,20 @@
       <c r="T12" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="13" spans="2:20" x14ac:dyDescent="0.45">
+      <c r="V12" t="s">
+        <v>78</v>
+      </c>
+      <c r="W12" t="s">
+        <v>82</v>
+      </c>
+      <c r="X12" t="s">
+        <v>83</v>
+      </c>
+      <c r="Y12" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="13" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B13" t="s">
         <v>78</v>
       </c>
@@ -921,10 +963,10 @@
         <v>78</v>
       </c>
       <c r="M13" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="N13" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="O13" t="s">
         <v>105</v>
@@ -941,8 +983,20 @@
       <c r="T13" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="14" spans="2:20" x14ac:dyDescent="0.45">
+      <c r="V13" t="s">
+        <v>78</v>
+      </c>
+      <c r="W13" t="s">
+        <v>89</v>
+      </c>
+      <c r="X13" t="s">
+        <v>90</v>
+      </c>
+      <c r="Y13" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="14" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B14" t="s">
         <v>78</v>
       </c>
@@ -971,10 +1025,10 @@
         <v>78</v>
       </c>
       <c r="M14" t="s">
-        <v>93</v>
+        <v>79</v>
       </c>
       <c r="N14" t="s">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="O14" t="s">
         <v>105</v>
@@ -991,8 +1045,20 @@
       <c r="T14" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="15" spans="2:20" x14ac:dyDescent="0.45">
+      <c r="V14" t="s">
+        <v>78</v>
+      </c>
+      <c r="W14" t="s">
+        <v>84</v>
+      </c>
+      <c r="X14" t="s">
+        <v>85</v>
+      </c>
+      <c r="Y14" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="15" spans="2:25" x14ac:dyDescent="0.45">
       <c r="G15" t="s">
         <v>78</v>
       </c>
@@ -1009,10 +1075,10 @@
         <v>78</v>
       </c>
       <c r="M15" t="s">
-        <v>82</v>
+        <v>106</v>
       </c>
       <c r="N15" t="s">
-        <v>83</v>
+        <v>107</v>
       </c>
       <c r="O15" t="s">
         <v>105</v>
@@ -1029,8 +1095,20 @@
       <c r="T15" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="16" spans="2:20" x14ac:dyDescent="0.45">
+      <c r="V15" t="s">
+        <v>78</v>
+      </c>
+      <c r="W15" t="s">
+        <v>93</v>
+      </c>
+      <c r="X15" t="s">
+        <v>94</v>
+      </c>
+      <c r="Y15" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="16" spans="2:25" x14ac:dyDescent="0.45">
       <c r="G16" t="s">
         <v>78</v>
       </c>
@@ -1047,10 +1125,10 @@
         <v>78</v>
       </c>
       <c r="M16" t="s">
-        <v>89</v>
+        <v>108</v>
       </c>
       <c r="N16" t="s">
-        <v>90</v>
+        <v>109</v>
       </c>
       <c r="O16" t="s">
         <v>105</v>
@@ -1067,6 +1145,18 @@
       <c r="T16" t="s">
         <v>112</v>
       </c>
+      <c r="V16" t="s">
+        <v>78</v>
+      </c>
+      <c r="W16" t="s">
+        <v>95</v>
+      </c>
+      <c r="X16" t="s">
+        <v>96</v>
+      </c>
+      <c r="Y16" t="s">
+        <v>113</v>
+      </c>
     </row>
     <row r="17" spans="7:15" x14ac:dyDescent="0.45">
       <c r="G17" t="s">
@@ -1085,10 +1175,10 @@
         <v>78</v>
       </c>
       <c r="M17" t="s">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="N17" t="s">
-        <v>107</v>
+        <v>85</v>
       </c>
       <c r="O17" t="s">
         <v>105</v>
@@ -1111,10 +1201,10 @@
         <v>78</v>
       </c>
       <c r="M18" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="N18" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="O18" t="s">
         <v>105</v>
@@ -1137,10 +1227,10 @@
         <v>78</v>
       </c>
       <c r="M19" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="N19" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="O19" t="s">
         <v>105</v>
@@ -1163,10 +1253,10 @@
         <v>78</v>
       </c>
       <c r="M20" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="N20" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="O20" t="s">
         <v>105</v>
@@ -1189,10 +1279,10 @@
         <v>78</v>
       </c>
       <c r="M21" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="N21" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="O21" t="s">
         <v>105</v>
@@ -1215,10 +1305,10 @@
         <v>78</v>
       </c>
       <c r="M22" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="N22" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="O22" t="s">
         <v>105</v>
@@ -1229,10 +1319,10 @@
         <v>78</v>
       </c>
       <c r="M23" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="N23" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="O23" t="s">
         <v>105</v>
@@ -1243,10 +1333,10 @@
         <v>78</v>
       </c>
       <c r="M24" t="s">
-        <v>110</v>
+        <v>91</v>
       </c>
       <c r="N24" t="s">
-        <v>111</v>
+        <v>92</v>
       </c>
       <c r="O24" t="s">
         <v>105</v>
@@ -1257,10 +1347,10 @@
         <v>78</v>
       </c>
       <c r="M25" t="s">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="N25" t="s">
-        <v>96</v>
+        <v>111</v>
       </c>
       <c r="O25" t="s">
         <v>105</v>

--- a/VerveStacks_HRV_grids_kan10/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_HRV_grids_kan10/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_HRV_grids_kan10\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D6AB895F-B599-4116-AA74-B9AD03C78F4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A497B1EC-50FF-4BE2-8807-F043CEFCCDB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -364,16 +364,16 @@
     <t>at grid node - Sibenik_HRV</t>
   </si>
   <si>
+    <t>Rijeka_HRV</t>
+  </si>
+  <si>
+    <t>at grid node - Rijeka_HRV</t>
+  </si>
+  <si>
     <t>KastelStari_HRV</t>
   </si>
   <si>
     <t>at grid node - KastelStari_HRV</t>
-  </si>
-  <si>
-    <t>Rijeka_HRV</t>
-  </si>
-  <si>
-    <t>at grid node - Rijeka_HRV</t>
   </si>
   <si>
     <t>h_demand</t>
@@ -839,10 +839,10 @@
         <v>78</v>
       </c>
       <c r="M11" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="N11" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="O11" t="s">
         <v>105</v>
@@ -963,10 +963,10 @@
         <v>78</v>
       </c>
       <c r="M13" t="s">
-        <v>89</v>
+        <v>106</v>
       </c>
       <c r="N13" t="s">
-        <v>90</v>
+        <v>107</v>
       </c>
       <c r="O13" t="s">
         <v>105</v>
@@ -1025,10 +1025,10 @@
         <v>78</v>
       </c>
       <c r="M14" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="N14" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="O14" t="s">
         <v>105</v>
@@ -1075,10 +1075,10 @@
         <v>78</v>
       </c>
       <c r="M15" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="N15" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="O15" t="s">
         <v>105</v>
@@ -1125,10 +1125,10 @@
         <v>78</v>
       </c>
       <c r="M16" t="s">
-        <v>108</v>
+        <v>79</v>
       </c>
       <c r="N16" t="s">
-        <v>109</v>
+        <v>80</v>
       </c>
       <c r="O16" t="s">
         <v>105</v>
@@ -1175,10 +1175,10 @@
         <v>78</v>
       </c>
       <c r="M17" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="N17" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="O17" t="s">
         <v>105</v>
@@ -1201,10 +1201,10 @@
         <v>78</v>
       </c>
       <c r="M18" t="s">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="N18" t="s">
-        <v>104</v>
+        <v>83</v>
       </c>
       <c r="O18" t="s">
         <v>105</v>
@@ -1227,10 +1227,10 @@
         <v>78</v>
       </c>
       <c r="M19" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="N19" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="O19" t="s">
         <v>105</v>
@@ -1253,10 +1253,10 @@
         <v>78</v>
       </c>
       <c r="M20" t="s">
-        <v>82</v>
+        <v>108</v>
       </c>
       <c r="N20" t="s">
-        <v>83</v>
+        <v>109</v>
       </c>
       <c r="O20" t="s">
         <v>105</v>
@@ -1279,10 +1279,10 @@
         <v>78</v>
       </c>
       <c r="M21" t="s">
-        <v>86</v>
+        <v>103</v>
       </c>
       <c r="N21" t="s">
-        <v>87</v>
+        <v>104</v>
       </c>
       <c r="O21" t="s">
         <v>105</v>
@@ -1319,10 +1319,10 @@
         <v>78</v>
       </c>
       <c r="M23" t="s">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="N23" t="s">
-        <v>96</v>
+        <v>111</v>
       </c>
       <c r="O23" t="s">
         <v>105</v>
@@ -1333,10 +1333,10 @@
         <v>78</v>
       </c>
       <c r="M24" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="N24" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="O24" t="s">
         <v>105</v>
@@ -1347,10 +1347,10 @@
         <v>78</v>
       </c>
       <c r="M25" t="s">
-        <v>110</v>
+        <v>89</v>
       </c>
       <c r="N25" t="s">
-        <v>111</v>
+        <v>90</v>
       </c>
       <c r="O25" t="s">
         <v>105</v>

--- a/VerveStacks_HRV_grids_kan10/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_HRV_grids_kan10/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_HRV_grids_kan10\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A497B1EC-50FF-4BE2-8807-F043CEFCCDB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DE70C7B9-7D93-459C-99FF-C07DDACB5554}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -355,25 +355,25 @@
     <t>at grid node - Knin_HRV</t>
   </si>
   <si>
+    <t>Rijeka_HRV</t>
+  </si>
+  <si>
+    <t>at grid node - Rijeka_HRV</t>
+  </si>
+  <si>
     <t>e_demand,ev_battery,H2prd_Elc_PEM,H2prd_Elc_ALK</t>
   </si>
   <si>
+    <t>KastelStari_HRV</t>
+  </si>
+  <si>
+    <t>at grid node - KastelStari_HRV</t>
+  </si>
+  <si>
     <t>Sibenik_HRV</t>
   </si>
   <si>
     <t>at grid node - Sibenik_HRV</t>
-  </si>
-  <si>
-    <t>Rijeka_HRV</t>
-  </si>
-  <si>
-    <t>at grid node - Rijeka_HRV</t>
-  </si>
-  <si>
-    <t>KastelStari_HRV</t>
-  </si>
-  <si>
-    <t>at grid node - KastelStari_HRV</t>
   </si>
   <si>
     <t>h_demand</t>
@@ -839,13 +839,13 @@
         <v>78</v>
       </c>
       <c r="M11" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="N11" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="O11" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="Q11" t="s">
         <v>78</v>
@@ -901,13 +901,13 @@
         <v>78</v>
       </c>
       <c r="M12" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="N12" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="O12" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="Q12" t="s">
         <v>78</v>
@@ -963,13 +963,13 @@
         <v>78</v>
       </c>
       <c r="M13" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="N13" t="s">
+        <v>98</v>
+      </c>
+      <c r="O13" t="s">
         <v>107</v>
-      </c>
-      <c r="O13" t="s">
-        <v>105</v>
       </c>
       <c r="Q13" t="s">
         <v>78</v>
@@ -1025,13 +1025,13 @@
         <v>78</v>
       </c>
       <c r="M14" t="s">
-        <v>86</v>
+        <v>103</v>
       </c>
       <c r="N14" t="s">
-        <v>87</v>
+        <v>104</v>
       </c>
       <c r="O14" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="Q14" t="s">
         <v>78</v>
@@ -1075,13 +1075,13 @@
         <v>78</v>
       </c>
       <c r="M15" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="N15" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="O15" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="Q15" t="s">
         <v>78</v>
@@ -1125,13 +1125,13 @@
         <v>78</v>
       </c>
       <c r="M16" t="s">
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="N16" t="s">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="O16" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="Q16" t="s">
         <v>78</v>
@@ -1175,13 +1175,13 @@
         <v>78</v>
       </c>
       <c r="M17" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="N17" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="O17" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="18" spans="7:15" x14ac:dyDescent="0.45">
@@ -1207,7 +1207,7 @@
         <v>83</v>
       </c>
       <c r="O18" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="19" spans="7:15" x14ac:dyDescent="0.45">
@@ -1227,13 +1227,13 @@
         <v>78</v>
       </c>
       <c r="M19" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="N19" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="O19" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="20" spans="7:15" x14ac:dyDescent="0.45">
@@ -1253,13 +1253,13 @@
         <v>78</v>
       </c>
       <c r="M20" t="s">
-        <v>108</v>
+        <v>91</v>
       </c>
       <c r="N20" t="s">
-        <v>109</v>
+        <v>92</v>
       </c>
       <c r="O20" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="21" spans="7:15" x14ac:dyDescent="0.45">
@@ -1279,13 +1279,13 @@
         <v>78</v>
       </c>
       <c r="M21" t="s">
-        <v>103</v>
+        <v>79</v>
       </c>
       <c r="N21" t="s">
-        <v>104</v>
+        <v>80</v>
       </c>
       <c r="O21" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="22" spans="7:15" x14ac:dyDescent="0.45">
@@ -1305,13 +1305,13 @@
         <v>78</v>
       </c>
       <c r="M22" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="N22" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="O22" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="23" spans="7:15" x14ac:dyDescent="0.45">
@@ -1319,13 +1319,13 @@
         <v>78</v>
       </c>
       <c r="M23" t="s">
-        <v>110</v>
+        <v>86</v>
       </c>
       <c r="N23" t="s">
-        <v>111</v>
+        <v>87</v>
       </c>
       <c r="O23" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="24" spans="7:15" x14ac:dyDescent="0.45">
@@ -1333,13 +1333,13 @@
         <v>78</v>
       </c>
       <c r="M24" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="N24" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="O24" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="25" spans="7:15" x14ac:dyDescent="0.45">
@@ -1347,13 +1347,13 @@
         <v>78</v>
       </c>
       <c r="M25" t="s">
-        <v>89</v>
+        <v>110</v>
       </c>
       <c r="N25" t="s">
-        <v>90</v>
+        <v>111</v>
       </c>
       <c r="O25" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
   </sheetData>
